--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_MOVISTAR ESTUDIANTES.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_MOVISTAR ESTUDIANTES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:X15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3677</v>
+        <v>12.7863</v>
       </c>
       <c r="E2" t="n">
-        <v>6.570399999999999</v>
+        <v>12.5213</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7973999999999999</v>
+        <v>0.2649999999999998</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4792</v>
+        <v>7.396699999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1966000000000001</v>
+        <v>-2.0644</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6758</v>
+        <v>9.461</v>
       </c>
       <c r="J2" t="n">
-        <v>5.2556</v>
+        <v>15.4443</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3263</v>
+        <v>5.368</v>
       </c>
       <c r="L2" t="n">
-        <v>1.9293</v>
+        <v>10.0763</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.7764</v>
+        <v>-8.047699999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-3.5229</v>
+        <v>-7.4325</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7465999999999999</v>
+        <v>-0.6151000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>3.201</v>
+        <v>3.5053</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.4001</v>
+        <v>-5.257899999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>3.6011</v>
+        <v>8.763200000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7119</v>
+        <v>-0.2929000000000002</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9442999999999999</v>
+        <v>-1.8874</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2325</v>
+        <v>1.5944</v>
       </c>
       <c r="V2" t="n">
-        <v>2.3995</v>
+        <v>2.1773</v>
       </c>
       <c r="W2" t="n">
-        <v>2.6593</v>
+        <v>4.2221</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2598</v>
+        <v>-2.0449</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. SOLA IDRISU</t>
+          <t>M. LAGUNA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>7.3328</v>
+        <v>11.9752</v>
       </c>
       <c r="E3" t="n">
-        <v>6.203799999999999</v>
+        <v>6.364100000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>1.129</v>
+        <v>5.6111</v>
       </c>
       <c r="G3" t="n">
-        <v>7.8783</v>
+        <v>10.7715</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3416</v>
+        <v>-0.07830000000000004</v>
       </c>
       <c r="I3" t="n">
-        <v>5.5367</v>
+        <v>10.8498</v>
       </c>
       <c r="J3" t="n">
-        <v>8.8552</v>
+        <v>7.4131</v>
       </c>
       <c r="K3" t="n">
-        <v>4.6004</v>
+        <v>0.4979</v>
       </c>
       <c r="L3" t="n">
-        <v>4.2546</v>
+        <v>6.9151</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9768000000000001</v>
+        <v>3.3584</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.2589</v>
+        <v>-0.576</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2821</v>
+        <v>3.9345</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6002</v>
+        <v>1.1685</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.401</v>
+        <v>-2.1421</v>
       </c>
       <c r="R3" t="n">
-        <v>2.8008</v>
+        <v>3.3105</v>
       </c>
       <c r="S3" t="n">
-        <v>-3.1243</v>
+        <v>-0.9580000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-2.4293</v>
+        <v>-1.0178</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6950000000000001</v>
+        <v>0.0600999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>3.1789</v>
+        <v>0.9931999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>3.1789</v>
+        <v>2.1111</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.118</v>
       </c>
     </row>
     <row r="4">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0144</v>
+        <v>11.3195</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07180000000000009</v>
+        <v>10.4907</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9425</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0927</v>
+        <v>-3.1921</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1374000000000001</v>
+        <v>-2.4024</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9552999999999999</v>
+        <v>-0.7898000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6123</v>
+        <v>3.0624</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1323</v>
+        <v>1.9276</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4799</v>
+        <v>1.1347</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5194999999999999</v>
+        <v>-6.2545</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.995</v>
+        <v>-4.3299</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4754</v>
+        <v>-1.9246</v>
       </c>
       <c r="P4" t="n">
-        <v>-5.4016</v>
+        <v>-5.258</v>
       </c>
       <c r="Q4" t="n">
-        <v>-7.4021</v>
+        <v>-11.1001</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0005</v>
+        <v>5.842000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>5.9831</v>
+        <v>15.9156</v>
       </c>
       <c r="T4" t="n">
-        <v>5.002</v>
+        <v>12.4015</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9811</v>
+        <v>3.5141</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3401000000000001</v>
+        <v>3.8541</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8597</v>
+        <v>6.1268</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5196</v>
+        <v>-2.2729</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. LAGUNA RODRIGUEZ</t>
+          <t>G. PEREZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2322</v>
+        <v>7.1991</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3089</v>
+        <v>7.088699999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5411</v>
+        <v>0.1103999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9144</v>
+        <v>8.689499999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2227999999999999</v>
+        <v>0.3876999999999998</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1372</v>
+        <v>8.3019</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8112</v>
+        <v>11.2902</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3217</v>
+        <v>3.9466</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4894</v>
+        <v>7.3436</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1032</v>
+        <v>-2.6007</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5445</v>
+        <v>-3.559</v>
       </c>
       <c r="O5" t="n">
-        <v>1.6478</v>
+        <v>0.9582999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0002</v>
+        <v>-4.479</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0003</v>
+        <v>-9.9316</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0005</v>
+        <v>5.452500000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9032</v>
+        <v>-1.2335</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1198</v>
+        <v>-1.4415</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7833</v>
+        <v>0.2081</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7793999999999999</v>
+        <v>4.2221</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>7.1716</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.7793999999999999</v>
+        <v>-2.9495</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>I. MONTERO ISLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7826999999999997</v>
+        <v>6.7677</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4352</v>
+        <v>4.2969</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6523000000000001</v>
+        <v>2.4709</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1629</v>
+        <v>5.313499999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2771</v>
+        <v>2.3532</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1141</v>
+        <v>2.9603</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3033</v>
+        <v>5.0749</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0233</v>
+        <v>2.4478</v>
       </c>
       <c r="L6" t="n">
-        <v>0.28</v>
+        <v>2.6271</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4662</v>
+        <v>0.2386000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.3004</v>
+        <v>-0.09460000000000007</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8341999999999999</v>
+        <v>0.3331</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.8002</v>
+        <v>-0.3894000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.0009</v>
+        <v>-3.1158</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2006</v>
+        <v>2.7264</v>
       </c>
       <c r="S6" t="n">
-        <v>0.806</v>
+        <v>0.8875999999999998</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1264999999999999</v>
+        <v>-0.3839</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9325</v>
+        <v>1.2714</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9562</v>
       </c>
       <c r="W6" t="n">
-        <v>3.2592</v>
+        <v>2.7216</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.3193</v>
+        <v>-1.7654</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. APARICIO RODRÍGUEZ</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5999</v>
+        <v>6.4497</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5999</v>
+        <v>4.9719</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.4778</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5999</v>
+        <v>2.9608</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.4982000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5999</v>
+        <v>2.4625</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5999</v>
+        <v>3.8825</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2.9098</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5999</v>
+        <v>0.9727</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-0.9218000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-2.4115</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.4899</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-7.0106</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>4.8684</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>5.2484</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.5469</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.7016</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3825999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>4.5532</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-4.1705</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. ROBLES LLANOS</t>
+          <t>M. SOLA IDRISU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2554</v>
+        <v>3.9313</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5277</v>
+        <v>5.6652</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2723</v>
+        <v>-1.7339</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3845000000000001</v>
+        <v>8.1927</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2042999999999999</v>
+        <v>4.264</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5888</v>
+        <v>3.9287</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2187</v>
+        <v>13.8259</v>
       </c>
       <c r="K8" t="n">
-        <v>2.7901</v>
+        <v>8.351800000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5713000000000004</v>
+        <v>5.474299999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8341</v>
+        <v>-5.6333</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.9944</v>
+        <v>-4.0878</v>
       </c>
       <c r="O8" t="n">
-        <v>1.1603</v>
+        <v>-1.5455</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6002000000000001</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.401</v>
+        <v>-8.178900000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>2.8008</v>
+        <v>5.8422</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5682</v>
+        <v>-4.6609</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3885999999999999</v>
+        <v>-4.4834</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1796</v>
+        <v>-0.1772</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0392</v>
+        <v>2.7362</v>
       </c>
       <c r="W8" t="n">
-        <v>3.0986</v>
+        <v>4.5016</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.0594</v>
+        <v>-1.7654</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. MONTERO ISLA</t>
+          <t>M. LORENZO SALCEDA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1411</v>
+        <v>1.9684</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8312999999999999</v>
+        <v>2.0437</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9725</v>
+        <v>-0.07540000000000008</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1799</v>
+        <v>1.2714</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7292000000000001</v>
+        <v>-0.445</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4506</v>
+        <v>1.7164</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5454</v>
+        <v>2.4147</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9797</v>
+        <v>0.2668</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5655999999999999</v>
+        <v>2.1479</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3654999999999999</v>
+        <v>-1.1434</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2504</v>
+        <v>-0.7118</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1149999999999999</v>
+        <v>-0.4315000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4001</v>
+        <v>0.7789</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2192</v>
+        <v>-0.1482</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5733999999999999</v>
+        <v>-0.371</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7926</v>
+        <v>0.2227</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8596999999999999</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.7997</v>
+        <v>0.06619999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. LORENZO SALCEDA</t>
+          <t>H. APARICIO RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,43 +1186,43 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3999</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="E10" t="n">
+        <v>0.9157999999999999</v>
+      </c>
+      <c r="F10" t="n">
         <v>0</v>
       </c>
-      <c r="F10" t="n">
-        <v>-0.3999</v>
-      </c>
       <c r="G10" t="n">
-        <v>-0.3999</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="H10" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.6079</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.9157999999999999</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.6079</v>
+      </c>
+      <c r="M10" t="n">
         <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-0.3999</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>-0.3999</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3999</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. APARICIO RODRIGUEZ</t>
+          <t>P. ROBLES LLANOS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8394999999999999</v>
+        <v>-0.2875000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.06079999999999997</v>
+        <v>4.1308</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7787000000000001</v>
+        <v>-4.4183</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1547</v>
+        <v>-3.565199999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2835000000000001</v>
+        <v>-1.5611</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8711000000000001</v>
+        <v>-2.0042</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2307</v>
+        <v>2.1748</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4035</v>
+        <v>3.5899</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6342</v>
+        <v>-1.415300000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.924</v>
+        <v>-5.7399</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6871</v>
+        <v>-5.1509</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2369000000000001</v>
+        <v>-0.589</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4002</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.2004</v>
+        <v>-8.178899999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6004</v>
+        <v>5.8422</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.4845</v>
+        <v>-2.3955</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2891</v>
+        <v>-1.2071</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1954</v>
+        <v>-1.1884</v>
       </c>
       <c r="V11" t="n">
-        <v>2.3995</v>
+        <v>8.010100000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>2.6593</v>
+        <v>11.3422</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2598</v>
+        <v>-3.3322</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. SANCHEZ PEREZ</t>
+          <t>H. APARICIO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4874</v>
+        <v>-4.7278</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8838</v>
+        <v>-5.2429</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3964</v>
+        <v>0.5151999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.6136</v>
+        <v>-3.6868</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6908</v>
+        <v>-1.8453</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.9228</v>
+        <v>-1.8416</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.839</v>
+        <v>-3.032</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3326</v>
+        <v>-1.1363</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.5063</v>
+        <v>-1.8958</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7746000000000001</v>
+        <v>-0.6548999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3581</v>
+        <v>-0.709</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5835</v>
+        <v>0.05409999999999993</v>
       </c>
       <c r="P12" t="n">
-        <v>0.8003</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.2004</v>
+        <v>-3.3105</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0005</v>
+        <v>2.921</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8456</v>
+        <v>-3.7557</v>
       </c>
       <c r="T12" t="n">
-        <v>0.636</v>
+        <v>-2.2324</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2096</v>
+        <v>-1.5231</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5196</v>
+        <v>3.1042</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5196</v>
+        <v>3.3321</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0392</v>
+        <v>-0.2279000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. PEREZ HERNANDEZ</t>
+          <t>V. NEGRE FABREGAT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,148 +1420,226 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.4947</v>
+        <v>-4.9478</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3871</v>
+        <v>-3.6249</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1076</v>
+        <v>-1.3229</v>
       </c>
       <c r="G13" t="n">
-        <v>2.295</v>
+        <v>-0.4778999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1615</v>
+        <v>-0.5173000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1335</v>
+        <v>0.03939999999999995</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2902</v>
+        <v>0.8625</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7265</v>
+        <v>-0.1925000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5637</v>
+        <v>1.055</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.9952</v>
+        <v>-1.3405</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.565</v>
+        <v>-0.3249</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5698</v>
+        <v>-1.0156</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.4009</v>
+        <v>-0.9737000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.0015</v>
+        <v>-2.9211</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6004</v>
+        <v>1.9473</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.129</v>
+        <v>-2.2751</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4755</v>
+        <v>-1.8458</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6534</v>
+        <v>-0.4292</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2598</v>
+        <v>-1.221</v>
       </c>
       <c r="W13" t="n">
-        <v>1.7997</v>
+        <v>0.2795</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.0595</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>D. SANCHEZ PEREZ</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MOVISTAR ESTUDIANTES</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-5.7691</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-5.0023</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.7667999999999999</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-8.751899999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-1.8304</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-6.9217</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-2.9395</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.8247</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-4.7642</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-5.8126</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-3.655</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-2.1575</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.7789</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-6.036799999999999</v>
+      </c>
+      <c r="R14" t="n">
+        <v>5.2577</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4.982900000000001</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.2456</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.7374</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-1.2211</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.7284</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-2.9495</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>MOVISTAR ESTUDIANTES</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>13.2225</v>
-      </c>
-      <c r="E14" t="n">
-        <v>13.5995</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-0.3769000000000005</v>
-      </c>
-      <c r="G14" t="n">
-        <v>12.4928</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.4946000000000002</v>
-      </c>
-      <c r="I14" t="n">
-        <v>11.9981</v>
-      </c>
-      <c r="J14" t="n">
-        <v>22.4221</v>
-      </c>
-      <c r="K14" t="n">
-        <v>16.9712</v>
-      </c>
-      <c r="L14" t="n">
-        <v>5.450600000000001</v>
-      </c>
-      <c r="M14" t="n">
-        <v>-9.929</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-16.4767</v>
-      </c>
-      <c r="O14" t="n">
-        <v>6.547899999999999</v>
-      </c>
-      <c r="P14" t="n">
-        <v>-6.001600000000002</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-27.008</v>
-      </c>
-      <c r="R14" t="n">
-        <v>21.0057</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-1.067199999999999</v>
-      </c>
-      <c r="T14" t="n">
-        <v>-0.7084999999999994</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-0.3583999999999998</v>
-      </c>
-      <c r="V14" t="n">
-        <v>7.798400000000001</v>
-      </c>
-      <c r="W14" t="n">
-        <v>18.894</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-11.0957</v>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>47.58079999999999</v>
+      </c>
+      <c r="E15" t="n">
+        <v>44.61899999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.9622</v>
+      </c>
+      <c r="G15" t="n">
+        <v>25.838</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-2.9332</v>
+      </c>
+      <c r="I15" t="n">
+        <v>28.7706</v>
+      </c>
+      <c r="J15" t="n">
+        <v>60.38959999999999</v>
+      </c>
+      <c r="K15" t="n">
+        <v>30.11</v>
+      </c>
+      <c r="L15" t="n">
+        <v>30.2793</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-34.5523</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-33.0429</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-1.5089</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-13.6315</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-67.18430000000001</v>
+      </c>
+      <c r="R15" t="n">
+        <v>53.5523</v>
+      </c>
+      <c r="S15" t="n">
+        <v>11.3147</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.3237</v>
+      </c>
+      <c r="U15" t="n">
+        <v>7.9919</v>
+      </c>
+      <c r="V15" t="n">
+        <v>24.0601</v>
+      </c>
+      <c r="W15" t="n">
+        <v>48.0902</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-24.0305</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_MOVISTAR ESTUDIANTES.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_MOVISTAR ESTUDIANTES.xlsx
@@ -565,13 +565,13 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>12.7863</v>
+        <v>15.8306</v>
       </c>
       <c r="E2" t="n">
-        <v>12.5213</v>
+        <v>16.2055</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2649999999999998</v>
+        <v>-0.3749</v>
       </c>
       <c r="G2" t="n">
         <v>7.396699999999999</v>
@@ -610,13 +610,13 @@
         <v>8.763200000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2929000000000002</v>
+        <v>2.7515</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.8874</v>
+        <v>1.7971</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5944</v>
+        <v>0.9543999999999998</v>
       </c>
       <c r="V2" t="n">
         <v>2.1773</v>
@@ -643,13 +643,13 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>11.9752</v>
+        <v>12.7658</v>
       </c>
       <c r="E3" t="n">
-        <v>6.364100000000001</v>
+        <v>6.8486</v>
       </c>
       <c r="F3" t="n">
-        <v>5.6111</v>
+        <v>5.9171</v>
       </c>
       <c r="G3" t="n">
         <v>10.7715</v>
@@ -688,13 +688,13 @@
         <v>3.3105</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9580000000000001</v>
+        <v>-0.1674</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0178</v>
+        <v>-0.5335000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0600999999999999</v>
+        <v>0.3660999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>0.9931999999999999</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. AMON BYSTROVA</t>
+          <t>G. PEREZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>11.3195</v>
+        <v>9.754</v>
       </c>
       <c r="E4" t="n">
-        <v>10.4907</v>
+        <v>8.669599999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8290999999999999</v>
+        <v>1.0844</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.1921</v>
+        <v>8.689499999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.4024</v>
+        <v>0.3876999999999998</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7898000000000001</v>
+        <v>8.3019</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0624</v>
+        <v>11.2902</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9276</v>
+        <v>3.9466</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1347</v>
+        <v>7.3436</v>
       </c>
       <c r="M4" t="n">
-        <v>-6.2545</v>
+        <v>-2.6007</v>
       </c>
       <c r="N4" t="n">
-        <v>-4.3299</v>
+        <v>-3.559</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.9246</v>
+        <v>0.9582999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>-5.258</v>
+        <v>-4.479</v>
       </c>
       <c r="Q4" t="n">
-        <v>-11.1001</v>
+        <v>-9.9316</v>
       </c>
       <c r="R4" t="n">
-        <v>5.842000000000001</v>
+        <v>5.452500000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>15.9156</v>
+        <v>1.3214</v>
       </c>
       <c r="T4" t="n">
-        <v>12.4015</v>
+        <v>0.1394</v>
       </c>
       <c r="U4" t="n">
-        <v>3.5141</v>
+        <v>1.182</v>
       </c>
       <c r="V4" t="n">
-        <v>3.8541</v>
+        <v>4.2221</v>
       </c>
       <c r="W4" t="n">
-        <v>6.1268</v>
+        <v>7.1716</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.2729</v>
+        <v>-2.9495</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. PEREZ HERNANDEZ</t>
+          <t>M. SOLA IDRISU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>7.1991</v>
+        <v>8.879099999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>7.088699999999999</v>
+        <v>9.9236</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1103999999999999</v>
+        <v>-1.0445</v>
       </c>
       <c r="G5" t="n">
-        <v>8.689499999999999</v>
+        <v>8.1927</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3876999999999998</v>
+        <v>4.264</v>
       </c>
       <c r="I5" t="n">
-        <v>8.3019</v>
+        <v>3.9287</v>
       </c>
       <c r="J5" t="n">
-        <v>11.2902</v>
+        <v>13.8259</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9466</v>
+        <v>8.351800000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>7.3436</v>
+        <v>5.474299999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.6007</v>
+        <v>-5.6333</v>
       </c>
       <c r="N5" t="n">
-        <v>-3.559</v>
+        <v>-4.0878</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9582999999999999</v>
+        <v>-1.5455</v>
       </c>
       <c r="P5" t="n">
-        <v>-4.479</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q5" t="n">
-        <v>-9.9316</v>
+        <v>-8.178900000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>5.452500000000001</v>
+        <v>5.8422</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2335</v>
+        <v>0.2870000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.4415</v>
+        <v>-0.2251</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2081</v>
+        <v>0.5119999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>4.2221</v>
+        <v>2.7362</v>
       </c>
       <c r="W5" t="n">
-        <v>7.1716</v>
+        <v>4.5016</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.9495</v>
+        <v>-1.7654</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>6.7677</v>
+        <v>6.3487</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2969</v>
+        <v>4.2212</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4709</v>
+        <v>2.1276</v>
       </c>
       <c r="G6" t="n">
         <v>5.313499999999999</v>
@@ -922,13 +922,13 @@
         <v>2.7264</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8875999999999998</v>
+        <v>0.4687000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3839</v>
+        <v>-0.4596</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2714</v>
+        <v>0.9280999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>0.9562</v>
@@ -955,13 +955,13 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>6.4497</v>
+        <v>3.1117</v>
       </c>
       <c r="E7" t="n">
-        <v>4.9719</v>
+        <v>1.9679</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4778</v>
+        <v>1.1439</v>
       </c>
       <c r="G7" t="n">
         <v>2.9608</v>
@@ -1000,13 +1000,13 @@
         <v>4.8684</v>
       </c>
       <c r="S7" t="n">
-        <v>5.2484</v>
+        <v>1.9105</v>
       </c>
       <c r="T7" t="n">
-        <v>3.5469</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>1.7016</v>
+        <v>1.3677</v>
       </c>
       <c r="V7" t="n">
         <v>0.3825999999999999</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. SOLA IDRISU</t>
+          <t>M. LORENZO SALCEDA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>3.9313</v>
+        <v>2.6777</v>
       </c>
       <c r="E8" t="n">
-        <v>5.6652</v>
+        <v>2.6418</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7339</v>
+        <v>0.03590000000000004</v>
       </c>
       <c r="G8" t="n">
-        <v>8.1927</v>
+        <v>1.2714</v>
       </c>
       <c r="H8" t="n">
-        <v>4.264</v>
+        <v>-0.445</v>
       </c>
       <c r="I8" t="n">
-        <v>3.9287</v>
+        <v>1.7164</v>
       </c>
       <c r="J8" t="n">
-        <v>13.8259</v>
+        <v>2.4147</v>
       </c>
       <c r="K8" t="n">
-        <v>8.351800000000001</v>
+        <v>0.2668</v>
       </c>
       <c r="L8" t="n">
-        <v>5.474299999999999</v>
+        <v>2.1479</v>
       </c>
       <c r="M8" t="n">
-        <v>-5.6333</v>
+        <v>-1.1434</v>
       </c>
       <c r="N8" t="n">
-        <v>-4.0878</v>
+        <v>-0.7118</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5455</v>
+        <v>-0.4315000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.3368</v>
+        <v>0.7789</v>
       </c>
       <c r="Q8" t="n">
-        <v>-8.178900000000001</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>5.8422</v>
+        <v>0.7789</v>
       </c>
       <c r="S8" t="n">
-        <v>-4.6609</v>
+        <v>0.5611</v>
       </c>
       <c r="T8" t="n">
-        <v>-4.4834</v>
+        <v>0.2271</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1772</v>
+        <v>0.3341</v>
       </c>
       <c r="V8" t="n">
-        <v>2.7362</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>4.5016</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7654</v>
+        <v>0.06619999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. LORENZO SALCEDA</t>
+          <t>P. ROBLES LLANOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9684</v>
+        <v>2.074899999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0437</v>
+        <v>5.797600000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.07540000000000008</v>
+        <v>-3.7227</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2714</v>
+        <v>-3.565199999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.445</v>
+        <v>-1.5611</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7164</v>
+        <v>-2.0042</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4147</v>
+        <v>2.1748</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2668</v>
+        <v>3.5899</v>
       </c>
       <c r="L9" t="n">
-        <v>2.1479</v>
+        <v>-1.415300000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1434</v>
+        <v>-5.7399</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7118</v>
+        <v>-5.1509</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4315000000000001</v>
+        <v>-0.589</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7789</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-8.178899999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7789</v>
+        <v>5.8422</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1482</v>
+        <v>-0.03300000000000003</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.371</v>
+        <v>0.4597</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2227</v>
+        <v>-0.4927</v>
       </c>
       <c r="V9" t="n">
-        <v>0.06619999999999999</v>
+        <v>8.010100000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>11.3422</v>
       </c>
       <c r="X9" t="n">
-        <v>0.06619999999999999</v>
+        <v>-3.3322</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. APARICIO RODRÍGUEZ</t>
+          <t>A. AMON BYSTROVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9157999999999999</v>
+        <v>1.5192</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9157999999999999</v>
+        <v>2.5885</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-1.0695</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9157999999999999</v>
+        <v>-3.1921</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3079</v>
+        <v>-2.4024</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6079</v>
+        <v>-0.7898000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9157999999999999</v>
+        <v>3.0624</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3079</v>
+        <v>1.9276</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6079</v>
+        <v>1.1347</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>-6.2545</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-4.3299</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-1.9246</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-5.258</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-11.1001</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>5.842000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>6.115</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>4.4993</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.6157</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>3.8541</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>6.1268</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.2729</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. ROBLES LLANOS</t>
+          <t>H. APARICIO RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2875000000000001</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>4.1308</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.4183</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.565199999999999</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5611</v>
+        <v>0.3079</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0042</v>
+        <v>0.6079</v>
       </c>
       <c r="J11" t="n">
-        <v>2.1748</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5899</v>
+        <v>0.3079</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.415300000000001</v>
+        <v>0.6079</v>
       </c>
       <c r="M11" t="n">
-        <v>-5.7399</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-5.1509</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.589</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.3368</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-8.178899999999999</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>5.8422</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.3955</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1884</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>8.010100000000001</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>11.3422</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.3322</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7278</v>
+        <v>-2.4827</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.2429</v>
+        <v>-4.1604</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5151999999999999</v>
+        <v>1.6777</v>
       </c>
       <c r="G12" t="n">
         <v>-3.6868</v>
@@ -1390,13 +1390,13 @@
         <v>2.921</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.7557</v>
+        <v>-1.5106</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.2324</v>
+        <v>-1.1499</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.5231</v>
+        <v>-0.3607</v>
       </c>
       <c r="V12" t="n">
         <v>3.1042</v>
@@ -1423,13 +1423,13 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.9478</v>
+        <v>-3.049</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.6249</v>
+        <v>-2.6659</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3229</v>
+        <v>-0.3831</v>
       </c>
       <c r="G13" t="n">
         <v>-0.4778999999999999</v>
@@ -1468,13 +1468,13 @@
         <v>1.9473</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.2751</v>
+        <v>-0.3764</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.8458</v>
+        <v>-0.8868</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4292</v>
+        <v>0.5105999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-1.221</v>
@@ -1501,13 +1501,13 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.7691</v>
+        <v>-7.271500000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.0023</v>
+        <v>-5.5524</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7667999999999999</v>
+        <v>-1.719</v>
       </c>
       <c r="G14" t="n">
         <v>-8.751899999999999</v>
@@ -1546,13 +1546,13 @@
         <v>5.2577</v>
       </c>
       <c r="S14" t="n">
-        <v>4.982900000000001</v>
+        <v>3.4806</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2456</v>
+        <v>1.6954</v>
       </c>
       <c r="U14" t="n">
-        <v>2.7374</v>
+        <v>1.785</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2211</v>
@@ -1579,25 +1579,25 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>47.58079999999999</v>
+        <v>51.07429999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>44.61899999999999</v>
+        <v>47.4014</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9622</v>
+        <v>3.672900000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>25.838</v>
+        <v>25.83799999999999</v>
       </c>
       <c r="H15" t="n">
         <v>-2.9332</v>
       </c>
       <c r="I15" t="n">
-        <v>28.7706</v>
+        <v>28.77059999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>60.38959999999999</v>
+        <v>60.38960000000001</v>
       </c>
       <c r="K15" t="n">
         <v>30.11</v>
@@ -1618,19 +1618,19 @@
         <v>-13.6315</v>
       </c>
       <c r="Q15" t="n">
-        <v>-67.18430000000001</v>
+        <v>-67.18429999999999</v>
       </c>
       <c r="R15" t="n">
         <v>53.5523</v>
       </c>
       <c r="S15" t="n">
-        <v>11.3147</v>
+        <v>14.8084</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3237</v>
+        <v>6.1059</v>
       </c>
       <c r="U15" t="n">
-        <v>7.9919</v>
+        <v>8.702300000000001</v>
       </c>
       <c r="V15" t="n">
         <v>24.0601</v>
